--- a/Miami_Heat_2025-26_stats.xlsx
+++ b/Miami_Heat_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,57 @@
       </c>
       <c r="O13" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>15</v>
+      </c>
+      <c r="N14" t="n">
+        <v>38</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1136,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,6 +1877,57 @@
       </c>
       <c r="O13" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1839,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2529,6 +2631,57 @@
       </c>
       <c r="O13" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2542,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3231,6 +3384,57 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3267,7 +3471,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.77777777777778</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="3">
@@ -3287,7 +3491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.75</v>
+        <v>17.53846153846154</v>
       </c>
     </row>
     <row r="5">
@@ -3297,7 +3501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>17.46153846153846</v>
       </c>
     </row>
     <row r="6">
@@ -3307,7 +3511,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.5</v>
+        <v>11.30769230769231</v>
       </c>
     </row>
     <row r="7">
@@ -3317,7 +3521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.5</v>
+        <v>10.84615384615385</v>
       </c>
     </row>
     <row r="8">
@@ -3327,27 +3531,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.916666666666666</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nikola Jović</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.583333333333334</v>
+        <v>9.923076923076923</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Nikola Jović</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.583333333333334</v>
+        <v>9.076923076923077</v>
       </c>
     </row>
     <row r="11">
@@ -3357,7 +3561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.083333333333333</v>
+        <v>5.923076923076923</v>
       </c>
     </row>
     <row r="12">
@@ -3377,7 +3581,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.333333333333333</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -3423,7 +3627,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.333333333333333</v>
+        <v>7.615384615384615</v>
       </c>
     </row>
     <row r="3">
@@ -3433,7 +3637,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.083333333333333</v>
+        <v>5.230769230769231</v>
       </c>
     </row>
     <row r="4">
@@ -3443,7 +3647,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.416666666666667</v>
+        <v>3.307692307692307</v>
       </c>
     </row>
     <row r="5">
@@ -3453,7 +3657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.083333333333333</v>
+        <v>3.153846153846154</v>
       </c>
     </row>
     <row r="6">
@@ -3473,7 +3677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.833333333333333</v>
+        <v>2.846153846153846</v>
       </c>
     </row>
     <row r="8">
@@ -3483,7 +3687,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.75</v>
+        <v>2.692307692307693</v>
       </c>
     </row>
     <row r="9">
@@ -3493,23 +3697,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.666666666666667</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Simone Fontecchio</t>
+          <t>Myron Gardner</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.083333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Myron Gardner</t>
+          <t>Simone Fontecchio</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3533,7 +3737,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="14">
@@ -3579,7 +3783,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.166666666666666</v>
+        <v>9.23076923076923</v>
       </c>
     </row>
     <row r="3">
@@ -3599,7 +3803,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.166666666666667</v>
+        <v>7.307692307692307</v>
       </c>
     </row>
     <row r="5">
@@ -3609,7 +3813,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.75</v>
+        <v>4.923076923076923</v>
       </c>
     </row>
     <row r="6">
@@ -3619,7 +3823,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.666666666666667</v>
+        <v>4.615384615384615</v>
       </c>
     </row>
     <row r="7">
@@ -3629,7 +3833,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="8">
@@ -3639,7 +3843,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.75</v>
+        <v>2.846153846153846</v>
       </c>
     </row>
     <row r="9">
@@ -3649,7 +3853,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.583333333333333</v>
+        <v>2.538461538461538</v>
       </c>
     </row>
     <row r="10">
@@ -3659,7 +3863,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.416666666666667</v>
+        <v>2.384615384615385</v>
       </c>
     </row>
     <row r="11">
@@ -3669,7 +3873,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.916666666666667</v>
+        <v>1.923076923076923</v>
       </c>
     </row>
     <row r="12">
@@ -3679,7 +3883,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.666666666666667</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -3735,7 +3939,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -3745,7 +3949,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2.538461538461538</v>
       </c>
     </row>
     <row r="4">
@@ -3765,17 +3969,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1.923076923076923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nikola Jović</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.166666666666667</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="7">
@@ -3785,23 +3989,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.083333333333333</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Myron Gardner</t>
+          <t>Nikola Jović</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.076923076923077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Myron Gardner</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3811,7 +4015,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3825,7 +4029,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.75</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="12">
@@ -3835,7 +4039,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="13">
@@ -3845,7 +4049,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -3869,7 +4073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4151,6 +4355,27 @@
         <v>246</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>132</v>
+      </c>
+      <c r="D14" t="n">
+        <v>140</v>
+      </c>
+      <c r="E14" t="n">
+        <v>272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
